--- a/dividends.xlsx
+++ b/dividends.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fileserver_D\TradeReview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFECD73-8F64-4E01-B3A0-A7EA87270444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB089F51-386F-4AEE-9136-8852B0A713AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="1230" windowWidth="22260" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -32,6 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -68,9 +71,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -373,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -408,20 +412,8 @@
       <c r="A4" s="1">
         <v>46283</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>46374</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>46387</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46464</v>
+      <c r="B4" s="2">
+        <v>1.88883</v>
       </c>
     </row>
   </sheetData>
